--- a/Result/profitability/2204.xlsx
+++ b/Result/profitability/2204.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.21625</v>
+        <v>1.28375</v>
       </c>
       <c r="N2" t="n">
-        <v>13.6675</v>
+        <v>13.54875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>1.00875</v>
+        <v>1.09125</v>
       </c>
       <c r="N3" t="n">
-        <v>13.20125</v>
+        <v>14.21625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.80875</v>
+        <v>0.9175000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>13.37625</v>
+        <v>13.7275</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-3.78</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1925000000000001</v>
+        <v>0.285</v>
       </c>
       <c r="N5" t="n">
-        <v>10.60875</v>
+        <v>10.65125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03250000000000008</v>
+        <v>0.10125</v>
       </c>
       <c r="N6" t="n">
-        <v>9.706250000000001</v>
+        <v>9.23875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1424999999999999</v>
+        <v>-0.08624999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>8.7525</v>
+        <v>9.391249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
         <v>0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3237499999999999</v>
+        <v>-0.21875</v>
       </c>
       <c r="N8" t="n">
-        <v>8.7675</v>
+        <v>8.925000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1520,7 +1520,7 @@
         <v>0.44</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4162499999999999</v>
+        <v>-0.41625</v>
       </c>
       <c r="N9" t="n">
         <v>7.5575</v>
@@ -1647,7 +1647,7 @@
         <v>0.23</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4174999999999999</v>
+        <v>-0.4175</v>
       </c>
       <c r="N10" t="n">
         <v>7.68875</v>
@@ -1776,7 +1776,7 @@
         <v>0.39</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3462499999999999</v>
+        <v>-0.34625</v>
       </c>
       <c r="N11" t="n">
         <v>7.96</v>
@@ -1903,10 +1903,10 @@
         <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2449999999999999</v>
+        <v>-0.245</v>
       </c>
       <c r="N12" t="n">
-        <v>8.05625</v>
+        <v>8.056249999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2030,7 +2030,7 @@
         <v>0.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3387500000000001</v>
+        <v>0.33875</v>
       </c>
       <c r="N13" t="n">
         <v>10.12625</v>
@@ -9339,13 +9339,13 @@
         <v>8450</v>
       </c>
       <c r="D71" t="n">
-        <v>6853</v>
+        <v>7161</v>
       </c>
       <c r="E71" t="n">
-        <v>1597</v>
+        <v>1290</v>
       </c>
       <c r="F71" t="n">
-        <v>18.9</v>
+        <v>15.26</v>
       </c>
       <c r="G71" t="n">
         <v>448</v>
@@ -9371,7 +9371,7 @@
         <v>1.8225</v>
       </c>
       <c r="N71" t="n">
-        <v>14.75</v>
+        <v>14.295</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9383,7 +9383,7 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -9404,10 +9404,10 @@
         <v>0.1130434782608696</v>
       </c>
       <c r="Y71" t="n">
-        <v>6.109999999999999</v>
+        <v>2.470000000000001</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.4777169663799843</v>
+        <v>0.1931196247068023</v>
       </c>
       <c r="AA71" t="n">
         <v>-0.9299999999999999</v>
@@ -9416,10 +9416,10 @@
         <v>-0.420814479638009</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.909999999999998</v>
+        <v>-0.7300000000000004</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.1819887429643525</v>
+        <v>-0.0456535334584115</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -9431,14 +9431,14 @@
         <v>1</v>
       </c>
       <c r="AH71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>EPS衰退 / 毛利率成長</t>
+          <t>EPS衰退 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK71" t="n">
@@ -9466,13 +9466,13 @@
         <v>7560</v>
       </c>
       <c r="D72" t="n">
-        <v>6131</v>
+        <v>5823</v>
       </c>
       <c r="E72" t="n">
-        <v>1429</v>
+        <v>1737</v>
       </c>
       <c r="F72" t="n">
-        <v>18.91</v>
+        <v>22.98</v>
       </c>
       <c r="G72" t="n">
         <v>340</v>
@@ -9498,7 +9498,7 @@
         <v>1.69875</v>
       </c>
       <c r="N72" t="n">
-        <v>15.14375</v>
+        <v>15.1975</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9531,10 +9531,10 @@
         <v>0.1484375</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.01000000000000156</v>
+        <v>7.720000000000001</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.0005291005291006012</v>
+        <v>0.5058977719528179</v>
       </c>
       <c r="AA72" t="n">
         <v>-0.01000000000000001</v>
@@ -9543,10 +9543,10 @@
         <v>-0.006756756756756799</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.359999999999999</v>
+        <v>6.43</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.1425981873111781</v>
+        <v>0.3885196374622357</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9625,7 +9625,7 @@
         <v>1.60125</v>
       </c>
       <c r="N73" t="n">
-        <v>14.56875</v>
+        <v>14.6225</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -9658,10 +9658,10 @@
         <v>0.06802721088435382</v>
       </c>
       <c r="Y73" t="n">
-        <v>-8.85</v>
+        <v>-12.92</v>
       </c>
       <c r="Z73" t="n">
-        <v>-0.4680063458487572</v>
+        <v>-0.5622280243690165</v>
       </c>
       <c r="AA73" t="n">
         <v>0.21</v>
@@ -9752,7 +9752,7 @@
         <v>1.4625</v>
       </c>
       <c r="N74" t="n">
-        <v>14.32375</v>
+        <v>14.3775</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8641</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7330</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1311</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>489</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.66%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>459</v>
+      </c>
+      <c r="J75" t="n">
+        <v>948</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.43875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.275</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7118644067796611</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09058231488138024</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.08999999999999986</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.005897771952817821</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
